--- a/inst/plantillas/plantilla_une689.xlsx
+++ b/inst/plantillas/plantilla_une689.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agentes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mediciones" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Efectos_aditivos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Measurements" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Additive_effects" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -535,14 +535,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>expoquimR · Plantilla UNE-EN 689 · Hoja 1: Agentes</t>
+          <t>expoquimR · UNE-EN 689 Template · Sheet 1: Agents</t>
         </is>
       </c>
     </row>
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Define aqui cada agente quimico con su VLA. El campo 'agente' debe coincidir exactamente con el usado en la hoja Mediciones.</t>
+          <t>Define each chemical agent here with its VLA. The 'agent' field must match exactly the one used in the Measurements sheet.</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>agente</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -561,14 +561,14 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>descripcion</t>
+          <t>description</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tolueno</t>
+          <t>Toluene</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
@@ -576,14 +576,14 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Disolvente organico aromatico</t>
+          <t>Aromatic organic solvent</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Xileno</t>
+          <t>Xylene</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
@@ -591,14 +591,14 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Disolvente organico aromatico</t>
+          <t>Aromatic organic solvent</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Plomo</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
@@ -606,14 +606,14 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Metal pesado</t>
+          <t>Heavy metal</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Manganeso</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
@@ -621,7 +621,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Metal de transicion</t>
+          <t>Transition metal</t>
         </is>
       </c>
     </row>
@@ -654,14 +654,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>expoquimR · Plantilla UNE-EN 689 · Hoja 2: Mediciones</t>
+          <t>expoquimR · UNE-EN 689 Template · Sheet 2: Measurements</t>
         </is>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Una fila por muestra. 'tipo': pre (jornada preliminar) o add (jornada adicional, solo si resultado preliminar fue NO DECISION). 'jornada': numero de jornada dentro de cada tipo para ese agente (1, 2, 3...). 'muestra': numero de muestra dentro de esa jornada (1, 2, 3). concentracion en mg/m3, tiempo en horas.</t>
+          <t>One row per sample. 'type': pre (preliminary day) or add (additional day, only if the preliminary result was NO DECISION). 'day': day number within each type for that agent (1, 2, 3...). 'sample': sample number within that day (1, 2, 3). concentration in mg/m3, time in hours.</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -673,39 +673,39 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>agente</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>tipo</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>jornada</t>
+          <t>day</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>muestra</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>concentracion_mg_m3</t>
+          <t>concentration_mg_m3</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>tiempo_h</t>
+          <t>time_h</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tolueno</t>
+          <t>Toluene</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Tolueno</t>
+          <t>Toluene</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Tolueno</t>
+          <t>Toluene</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Tolueno</t>
+          <t>Toluene</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Tolueno</t>
+          <t>Toluene</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -825,7 +825,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Tolueno</t>
+          <t>Toluene</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Tolueno</t>
+          <t>Toluene</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Tolueno</t>
+          <t>Toluene</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -897,7 +897,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Tolueno</t>
+          <t>Toluene</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -921,7 +921,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Xileno</t>
+          <t>Xylene</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Xileno</t>
+          <t>Xylene</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -969,7 +969,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Xileno</t>
+          <t>Xylene</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Plomo</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1017,7 +1017,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Plomo</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Plomo</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Plomo</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1089,7 +1089,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Plomo</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Plomo</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Manganeso</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1161,7 +1161,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Manganeso</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1185,7 +1185,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Manganeso</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Manganeso</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Manganeso</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Manganeso</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Xileno</t>
+          <t>Xylene</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1305,7 +1305,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Xileno</t>
+          <t>Xylene</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Xileno</t>
+          <t>Xylene</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1353,7 +1353,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Xileno</t>
+          <t>Xylene</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1400,14 +1400,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>expoquimR · Plantilla UNE-EN 689 · Hoja 3: Efectos aditivos (opcional)</t>
+          <t>expoquimR · UNE-EN 689 Template · Sheet 3: Additive effects (optional)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="50" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Opcional. Define grupos de agentes con el mismo organo diana para el calculo aditivo. 'grupo': numero de grupo (1, 2, 3...). 'agente': debe coincidir exactamente con la hoja Agentes. Pueden compartir agentes entre grupos.</t>
+          <t>Optional. Define groups of agents sharing the same target organ for the additive calculation. 'group': group number (1, 2, 3...). 'agent': must match exactly the Agents sheet. Agents can be shared across groups.</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -1416,17 +1416,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>grupo</t>
+          <t>group</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>agente</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>descripcion_grupo</t>
+          <t>group_description</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Tolueno</t>
+          <t>Toluene</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Efecto SNC (sistema nervioso central)</t>
+          <t>CNS effect (central nervous system)</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Xileno</t>
+          <t>Xylene</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Efecto SNC (sistema nervioso central)</t>
+          <t>CNS effect (central nervous system)</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Plomo</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Efecto hematopoyetico</t>
+          <t>Haematopoietic effect</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Manganeso</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Efecto hematopoyetico</t>
+          <t>Haematopoietic effect</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Manganeso</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Efecto SNC (manganeso tambien afecta al SNC)</t>
+          <t>CNS effect (manganese also affects the CNS)</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Tolueno</t>
+          <t>Toluene</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Efecto SNC (sistema nervioso central)</t>
+          <t>CNS effect (central nervous system)</t>
         </is>
       </c>
     </row>
